--- a/Сравнение эффективности алгоритмов.xlsx
+++ b/Сравнение эффективности алгоритмов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79535\Desktop\Диплом\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3534ED50-60C6-490D-B861-77DB3394F896}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CF74DC-995A-4E8C-9CF6-9BE0AB8C582A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="5" xr2:uid="{211160BF-2A63-4B5C-BAA6-6A02063159D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{211160BF-2A63-4B5C-BAA6-6A02063159D2}"/>
   </bookViews>
   <sheets>
     <sheet name="% занятых серверов" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Кол-во сервисов</t>
   </si>
@@ -100,6 +100,12 @@
   <si>
     <t>Функция приспособленности оптимального решения</t>
   </si>
+  <si>
+    <t>Максимальная заполненность CPU, %</t>
+  </si>
+  <si>
+    <t>Использование Cpu, %</t>
+  </si>
 </sst>
 </file>
 
@@ -123,7 +129,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -146,11 +152,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -182,6 +197,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1302,6 +1318,1040 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
+              <a:t>Использование </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cpu Windows </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>серверов</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Алгоритм BFD</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Сравнение заполняемости'!$G$3:$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>WIN_1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>WIN_2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>WIN_3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>LIN_4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>LIN_5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Сравнение заполняемости'!$M$3:$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>Основной</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F763-4BBA-AF67-BE498F7000B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Генетический алгоритм</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Сравнение заполняемости'!$G$3:$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>WIN_1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>WIN_2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>WIN_3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>LIN_4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>LIN_5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Сравнение заполняемости'!$N$3:$N$7</c:f>
+              <c:numCache>
+                <c:formatCode>Основной</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F763-4BBA-AF67-BE498F7000B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Сравнение заполняемости'!$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Алгоритм имитации отжига</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Сравнение заполняемости'!$G$3:$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>WIN_1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>WIN_2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>WIN_3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>LIN_4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>LIN_5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Сравнение заполняемости'!$O$3:$O$7</c:f>
+              <c:numCache>
+                <c:formatCode>Основной</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F763-4BBA-AF67-BE498F7000B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                  <a:alpha val="33000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="1202476959"/>
+        <c:axId val="1202480703"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1202476959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="Основной" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1202480703"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1202480703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="Основной" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1202476959"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Использование </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cpu Linux </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>серверов</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Алгоритм BFD</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Сравнение заполняемости'!$G$3:$G$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Сравнение заполняемости'!$G$6:$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>LIN_4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LIN_5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Сравнение заполняемости'!$M$3:$M$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Сравнение заполняемости'!$M$6:$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>Основной</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-783C-4583-8EF7-A93FD5691984}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Генетический алгоритм</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Сравнение заполняемости'!$G$3:$G$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Сравнение заполняемости'!$G$6:$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>LIN_4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LIN_5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Сравнение заполняемости'!$N$3:$N$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Сравнение заполняемости'!$N$6:$N$7</c:f>
+              <c:numCache>
+                <c:formatCode>Основной</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-783C-4583-8EF7-A93FD5691984}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Сравнение заполняемости'!$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Алгоритм имитации отжига</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Сравнение заполняемости'!$G$3:$G$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Сравнение заполняемости'!$G$6:$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>LIN_4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LIN_5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Сравнение заполняемости'!$O$3:$O$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Сравнение заполняемости'!$O$6:$O$7</c:f>
+              <c:numCache>
+                <c:formatCode>Основной</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-783C-4583-8EF7-A93FD5691984}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                  <a:alpha val="33000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="1202476959"/>
+        <c:axId val="1202480703"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1202476959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="Основной" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1202480703"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1202480703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="25"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="Основной" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1202476959"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t>Зависимость точности результата от вероятности мутации</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
@@ -1410,37 +2460,37 @@
                 <c:formatCode>0,00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>299.35483870967744</c:v>
+                  <c:v>115.05144771476429</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>126.8982630272953</c:v>
+                  <c:v>29.24144532184733</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40.347394540942929</c:v>
+                  <c:v>17.587939698492466</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.3672456575682332</c:v>
+                  <c:v>4.917444364680545</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6558,6 +7608,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
   <cs:axisTitle>
@@ -9787,6 +10917,1082 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" spc="20" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+            <a:alpha val="33000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" spc="20" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+            <a:alpha val="33000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10715,6 +12921,82 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Диаграмма 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD13060C-9542-4347-BB95-F91D84CBFB58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Диаграмма 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24E9338-E707-4C02-A471-F2CD2A7CDD49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11066,14 +13348,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="F1" s="15" t="s">
+      <c r="D1" s="16"/>
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
@@ -11195,14 +13477,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="F1" s="16" t="s">
+      <c r="D1" s="17"/>
+      <c r="F1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="16"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
@@ -11330,18 +13612,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="F1" s="16" t="s">
+      <c r="D1" s="17"/>
+      <c r="F1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="I1" s="16" t="s">
+      <c r="G1" s="17"/>
+      <c r="I1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
@@ -11593,12 +13875,12 @@
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
@@ -11728,9 +14010,9 @@
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C30" s="2"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
@@ -11871,19 +14153,19 @@
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -12047,7 +14329,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB825C20-96F5-47BD-A2E4-C53225734F7A}">
-  <dimension ref="B1:J7"/>
+  <dimension ref="B1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
@@ -12058,23 +14340,33 @@
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
     </row>
-    <row r="2" spans="2:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
@@ -12099,8 +14391,20 @@
       <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="L2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
@@ -12125,8 +14429,20 @@
       <c r="J3" s="1">
         <v>99</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="1">
+        <v>100</v>
+      </c>
+      <c r="N3" s="1">
+        <v>98</v>
+      </c>
+      <c r="O3" s="1">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -12151,8 +14467,20 @@
       <c r="J4" s="1">
         <v>58</v>
       </c>
+      <c r="L4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="1">
+        <v>50</v>
+      </c>
+      <c r="N4" s="1">
+        <v>49</v>
+      </c>
+      <c r="O4" s="1">
+        <v>38</v>
+      </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -12177,8 +14505,20 @@
       <c r="J5" s="1">
         <v>48</v>
       </c>
+      <c r="L5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="1">
+        <v>22</v>
+      </c>
+      <c r="N5" s="1">
+        <v>24</v>
+      </c>
+      <c r="O5" s="1">
+        <v>33</v>
+      </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -12203,8 +14543,20 @@
       <c r="J6" s="1">
         <v>81</v>
       </c>
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="1">
+        <v>14</v>
+      </c>
+      <c r="N6" s="1">
+        <v>21</v>
+      </c>
+      <c r="O6" s="1">
+        <v>18</v>
+      </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
@@ -12229,11 +14581,24 @@
       <c r="J7" s="1">
         <v>10</v>
       </c>
+      <c r="L7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="1">
+        <v>15</v>
+      </c>
+      <c r="N7" s="1">
+        <v>13</v>
+      </c>
+      <c r="O7" s="1">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -12243,16 +14608,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5C7700-9C78-47DF-8A2D-36AB2E00CFDE}">
-  <dimension ref="B2:E30"/>
+  <dimension ref="B2:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="60" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
@@ -12265,41 +14631,50 @@
       <c r="E2" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="11" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>0.55600000000000005</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="D3" s="1">
+        <v>89</v>
+      </c>
+      <c r="E3" s="1">
         <v>92</v>
       </c>
-      <c r="E3" s="1">
-        <v>83</v>
+      <c r="F3" s="1">
+        <v>92</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>0.748</v>
+        <v>1.012</v>
       </c>
       <c r="D4" s="1">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E4" s="1">
-        <v>89</v>
+        <v>94</v>
+      </c>
+      <c r="F4" s="1">
+        <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>1.0149999999999999</v>
+        <v>1.514</v>
       </c>
       <c r="D5" s="1">
         <v>96</v>
@@ -12307,70 +14682,65 @@
       <c r="E5" s="1">
         <v>94</v>
       </c>
+      <c r="F5" s="1">
+        <v>95</v>
+      </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>9</v>
       </c>
       <c r="C6" s="1">
-        <v>1.214</v>
+        <v>1.921</v>
       </c>
       <c r="D6" s="1">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" s="1">
-        <v>96</v>
+        <v>99</v>
+      </c>
+      <c r="F6" s="1">
+        <v>99</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>1.2350000000000001</v>
+        <v>2.1219999999999999</v>
       </c>
       <c r="D7" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="1">
         <v>99</v>
       </c>
+      <c r="F7" s="1">
+        <v>99</v>
+      </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="1">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="D8" s="1">
-        <v>98</v>
-      </c>
-      <c r="E8" s="1">
-        <v>99</v>
-      </c>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="1">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.548</v>
-      </c>
-      <c r="D9" s="1">
-        <v>99</v>
-      </c>
-      <c r="E9" s="1">
-        <v>99</v>
-      </c>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="13" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="75" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
         <v>17</v>
       </c>
@@ -12384,49 +14754,49 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>0.05</v>
       </c>
       <c r="C14" s="1">
-        <v>-40.17</v>
+        <v>-12.58</v>
       </c>
       <c r="D14" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E14" s="14">
         <f>((D14-C14)/D14)*100</f>
-        <v>299.35483870967744</v>
+        <v>115.05144771476429</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>0.1</v>
       </c>
       <c r="C15" s="1">
-        <v>-5.42</v>
+        <v>59.14</v>
       </c>
       <c r="D15" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" ref="E15:E24" si="0">((D15-C15)/D15)*100</f>
-        <v>126.8982630272953</v>
+        <v>29.24144532184733</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>0.2</v>
       </c>
       <c r="C16" s="1">
-        <v>12.02</v>
+        <v>68.88</v>
       </c>
       <c r="D16" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="0"/>
-        <v>40.347394540942929</v>
+        <v>17.587939698492466</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
@@ -12434,14 +14804,14 @@
         <v>0.3</v>
       </c>
       <c r="C17" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D17" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
@@ -12449,14 +14819,14 @@
         <v>0.4</v>
       </c>
       <c r="C18" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D18" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
@@ -12464,14 +14834,14 @@
         <v>0.5</v>
       </c>
       <c r="C19" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D19" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
@@ -12479,14 +14849,14 @@
         <v>0.6</v>
       </c>
       <c r="C20" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D20" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -12494,14 +14864,14 @@
         <v>0.7</v>
       </c>
       <c r="C21" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D21" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
@@ -12509,14 +14879,14 @@
         <v>0.8</v>
       </c>
       <c r="C22" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D22" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
@@ -12524,14 +14894,14 @@
         <v>0.9</v>
       </c>
       <c r="C23" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D23" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
@@ -12539,14 +14909,14 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>19.27</v>
+        <v>79.47</v>
       </c>
       <c r="D24" s="1">
-        <v>20.149999999999999</v>
+        <v>83.58</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="0"/>
-        <v>4.3672456575682332</v>
+        <v>4.917444364680545</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
